--- a/config/MODBUS_REGISTERS.xlsx
+++ b/config/MODBUS_REGISTERS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332"/>
+    <workbookView windowWidth="18569" windowHeight="11268"/>
   </bookViews>
   <sheets>
     <sheet name="北向" sheetId="1" r:id="rId1"/>
@@ -27,17 +27,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
     <t>寄存器地址</t>
   </si>
   <si>
+    <t>名称</t>
+  </si>
+  <si>
     <t>寄存器类型</t>
   </si>
   <si>
     <t>数据类型</t>
   </si>
   <si>
+    <t>字节序</t>
+  </si>
+  <si>
     <t>系数</t>
   </si>
   <si>
@@ -56,13 +62,34 @@
     <t>备注</t>
   </si>
   <si>
-    <t>HoldingRegisters</t>
-  </si>
-  <si>
-    <t>I16</t>
-  </si>
-  <si>
-    <t>own</t>
+    <t>A 相电压</t>
+  </si>
+  <si>
+    <t>InputRegisters</t>
+  </si>
+  <si>
+    <t>U16</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>pcs</t>
+  </si>
+  <si>
+    <t>pcsPortAPhaseVoltage</t>
+  </si>
+  <si>
+    <t>B 相电压</t>
+  </si>
+  <si>
+    <t>pcsPortBPhaseVoltage</t>
+  </si>
+  <si>
+    <t>C 相电压</t>
+  </si>
+  <si>
+    <t>pcsPortCPhaseVoltage</t>
   </si>
 </sst>
 </file>
@@ -686,7 +713,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -694,6 +721,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1221,15 +1251,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="2"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="15.034188034188" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.034188034188" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="9.11111111111111" style="2"/>
+    <col min="2" max="3" width="17.034188034188" style="2" customWidth="1"/>
+    <col min="4" max="9" width="9.11111111111111" style="2"/>
+    <col min="10" max="10" width="27.1880341880342" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1257,45 +1289,107 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="2">
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="2">
+      <c r="J2" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="2">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="3">
+        <v>2</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2">
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3">
         <v>0.1</v>
       </c>
-      <c r="E3" s="2">
+      <c r="G4" s="2">
         <v>0</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="3">
+        <v>3</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/config/MODBUS_REGISTERS.xlsx
+++ b/config/MODBUS_REGISTERS.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>寄存器地址</t>
   </si>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <t>pcsPortCPhaseVoltage</t>
+  </si>
+  <si>
+    <t>通讯诊断</t>
+  </si>
+  <si>
+    <t>communicationStatus</t>
   </si>
 </sst>
 </file>
@@ -1251,8 +1257,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="3"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="15.034188034188" style="2" customWidth="1"/>
     <col min="2" max="3" width="17.034188034188" style="2" customWidth="1"/>
@@ -1313,7 +1319,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="3">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1345,7 +1351,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="3">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -1377,7 +1383,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="3">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -1390,6 +1396,38 @@
       </c>
       <c r="J4" s="3" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="2">
+        <v>65535</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/config/MODBUS_REGISTERS.xlsx
+++ b/config/MODBUS_REGISTERS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268"/>
+    <workbookView windowWidth="22010" windowHeight="12332"/>
   </bookViews>
   <sheets>
     <sheet name="北向" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="32">
   <si>
     <t>寄存器地址</t>
   </si>
@@ -62,7 +62,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>A 相电压</t>
+    <t>EMU运行模式</t>
   </si>
   <si>
     <t>InputRegisters</t>
@@ -74,28 +74,55 @@
     <t>AB</t>
   </si>
   <si>
-    <t>pcs</t>
-  </si>
-  <si>
-    <t>pcsPortAPhaseVoltage</t>
-  </si>
-  <si>
-    <t>B 相电压</t>
-  </si>
-  <si>
-    <t>pcsPortBPhaseVoltage</t>
-  </si>
-  <si>
-    <t>C 相电压</t>
-  </si>
-  <si>
-    <t>pcsPortCPhaseVoltage</t>
-  </si>
-  <si>
-    <t>通讯诊断</t>
-  </si>
-  <si>
-    <t>communicationStatus</t>
+    <t>emu</t>
+  </si>
+  <si>
+    <t>operation_mode</t>
+  </si>
+  <si>
+    <t>EMU充放电许可</t>
+  </si>
+  <si>
+    <t>permission</t>
+  </si>
+  <si>
+    <t>EMU告警故障状态</t>
+  </si>
+  <si>
+    <t>health_status</t>
+  </si>
+  <si>
+    <t>充电SOC限制</t>
+  </si>
+  <si>
+    <t>HoldingRegisters</t>
+  </si>
+  <si>
+    <t>charge_soc_limit</t>
+  </si>
+  <si>
+    <t>放电SOC限制</t>
+  </si>
+  <si>
+    <t>discharge_soc_limit</t>
+  </si>
+  <si>
+    <t>计划曲线使能</t>
+  </si>
+  <si>
+    <t>planned_curve</t>
+  </si>
+  <si>
+    <t>EMU上电方式</t>
+  </si>
+  <si>
+    <t>emu_power</t>
+  </si>
+  <si>
+    <t>系统热管理模式</t>
+  </si>
+  <si>
+    <t>sys_tms_mode</t>
   </si>
 </sst>
 </file>
@@ -108,7 +135,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +147,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -269,7 +303,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -278,6 +312,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CDED7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -387,12 +439,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,112 +635,106 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -703,10 +743,10 @@
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -715,21 +755,39 @@
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1257,14 +1315,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="4"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="15.034188034188" style="2" customWidth="1"/>
-    <col min="2" max="3" width="17.034188034188" style="2" customWidth="1"/>
-    <col min="4" max="9" width="9.11111111111111" style="2"/>
-    <col min="10" max="10" width="27.1880341880342" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.11111111111111" style="2"/>
+    <col min="1" max="1" width="15.031746031746" style="4" customWidth="1"/>
+    <col min="2" max="3" width="17.031746031746" style="4" customWidth="1"/>
+    <col min="4" max="9" width="9.11111111111111" style="4"/>
+    <col min="10" max="10" width="27.1904761904762" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9.11111111111111" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
@@ -1302,24 +1360,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:11">
+      <c r="A2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="3">
-        <v>10</v>
+      <c r="F2" s="2">
+        <v>1</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1327,31 +1385,31 @@
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <v>1</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="3" s="2" customFormat="1" spans="1:11">
+      <c r="A3" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3">
-        <v>10</v>
+      <c r="F3" s="2">
+        <v>1</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -1359,31 +1417,31 @@
       <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <v>2</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="4" s="2" customFormat="1" spans="1:11">
+      <c r="A4" s="2">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="3">
-        <v>10</v>
+      <c r="F4" s="2">
+        <v>1</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -1391,43 +1449,171 @@
       <c r="H4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <v>3</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="2">
+    <row r="5" s="3" customFormat="1" spans="1:11">
+      <c r="A5" s="6">
+        <v>3000</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="J5" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="1:11">
+      <c r="A6" s="6">
+        <v>3001</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F6" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G6" s="3">
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="2">
-        <v>65535</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="I6" s="3">
+        <v>5</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" spans="1:11">
+      <c r="A7" s="6">
+        <v>3002</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>22</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="3">
+        <v>6</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="1:11">
+      <c r="A8" s="6">
+        <v>3003</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="3">
+        <v>7</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:11">
+      <c r="A9" s="6">
+        <v>3004</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="3">
+        <v>10</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
